--- a/course-design-2/outputs/tables/ch3/10_job_text_preprocessing_audit.xlsx
+++ b/course-design-2/outputs/tables/ch3/10_job_text_preprocessing_audit.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_文本缺失统计" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_岗位描述长度分布" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_文本分段成功率" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_技能提取覆盖率" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_技能标准名统计" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_技能别名命中统计" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_未识别高频技术词候选" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_薪资泄漏清除检查" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_技能特征覆盖统计" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_岗位方向识别统计" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_岗位大类技能覆盖率" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="01_文本缺失统计" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_岗位描述长度分布" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_文本分段成功率" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_技能提取覆盖率" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="05_技能标准名统计" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="06_技能别名命中统计" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="07_未识别高频技术词候选" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="08_薪资泄漏清除检查" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="11_技能特征覆盖统计" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="12_岗位方向识别统计" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="13_岗位大类技能覆盖率" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/course-design-2/outputs/tables/ch3/10_job_text_preprocessing_audit.xlsx
+++ b/course-design-2/outputs/tables/ch3/10_job_text_preprocessing_audit.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_文本缺失统计" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_岗位描述长度分布" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_文本分段成功率" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_技能提取覆盖率" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="05_技能标准名统计" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="06_技能别名命中统计" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="07_未识别高频技术词候选" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="08_薪资泄漏清除检查" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="11_技能特征覆盖统计" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="12_岗位方向识别统计" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="13_岗位大类技能覆盖率" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_文本缺失统计" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_岗位描述长度分布" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_文本分段成功率" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_技能提取覆盖率" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_技能标准名统计" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_技能别名命中统计" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_未识别高频技术词候选" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_薪资泄漏清除检查" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_技能特征覆盖统计" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_岗位方向识别统计" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_岗位大类技能覆盖率" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
